--- a/docs/package/05_Delivery/Upload_Templates/Reason_Code_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Reason_Code_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="58">
   <si>
     <t xml:space="preserve">Code</t>
   </si>
@@ -81,7 +81,7 @@
     <t xml:space="preserve">decline (quotation rejected or dropped), repudiation (claim rejected), lapse (renewal lapsed), refund, adjustment or non-materialise</t>
   </si>
   <si>
-    <t xml:space="preserve">decline, repudiation, lapse, refund, adjustment, non-materialise</t>
+    <t xml:space="preserve">decline, repudiation, lapse, refund, adjustment, non-materialise, reassignment, period_close, period_reopen, year_end_reverse, cas_print_void, cas_document_change, incentive_batch_reject, incentive_adjustment, year_end_cancel, remittance_reject, remittance_withdraw, remittance_cancel, remittance_revoke, remittance_off_cycle, remittance_line_exclude, exception_escalate, exception_resolve, exception_reopen, reconciliation_difference, reconciliation_unmatch, confirmation_difference, payment_duplicate_override, billing_reject, billing_cancel, sales_invoice_cancel, invoice_payment_cancel, delegation, delegation_end, sod_exception, access_review, access_change, pdc_cancel, pdc_bounce, receipt_reversal, receipt_reversal_reject, unapplied_refund, renewal_reassign, non_renewal, claim_cancel, claim_cash_reversal, talkbot_line_remove, talkbot_list_cancel, feature_change, feature_reject, policy_suspend, policy_reinstate, commission_share_change, commission_rate_change, commission_reversal, commission_wht_change, scheme_end</t>
   </si>
   <si>
     <t xml:space="preserve">context</t>
@@ -132,12 +132,6 @@
     <t xml:space="preserve">Master &gt; Insurance Management &gt; Reason Codes (no Upload button on this screen yet: a System Administrator uploads the file through the API route)</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/masters/reason-code/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -168,10 +162,10 @@
     <t xml:space="preserve">The rows under the header on the Data sheet are samples. Delete them before you upload your own data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dates and amounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter dates as YYYY-MM-DD and amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
+    <t xml:space="preserve">Amounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
   </si>
   <si>
     <t xml:space="preserve">What happens on errors</t>
@@ -189,10 +183,10 @@
     <t xml:space="preserve">Coded reasons of the decisions that have no master of their own. Cancellation reasons and write-off reasons have their own masters.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -200,7 +194,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -596,7 +590,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -692,24 +686,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="4" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="13">
       <c r="B13" s="4" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Reason_Code_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Reason_Code_Upload_Template.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">decline (quotation rejected or dropped), repudiation (claim rejected), lapse (renewal lapsed), refund, adjustment or non-materialise</t>
   </si>
   <si>
-    <t xml:space="preserve">decline, repudiation, lapse, refund, adjustment, non-materialise, reassignment, period_close, period_reopen, year_end_reverse, cas_print_void, cas_document_change, incentive_batch_reject, incentive_adjustment, year_end_cancel, remittance_reject, remittance_withdraw, remittance_cancel, remittance_revoke, remittance_off_cycle, remittance_line_exclude, exception_escalate, exception_resolve, exception_reopen, reconciliation_difference, reconciliation_unmatch, confirmation_difference, payment_duplicate_override, billing_reject, billing_cancel, sales_invoice_cancel, invoice_payment_cancel, delegation, delegation_end, sod_exception, access_review, data_load_reject, access_change, pdc_cancel, pdc_bounce, receipt_reversal, receipt_reversal_reject, unapplied_refund, renewal_reassign, non_renewal, claim_cancel, claim_cash_reversal, talkbot_line_remove, talkbot_list_cancel, feature_change, feature_reject, policy_suspend, policy_reinstate, policy_correction, policy_correction_reject, endorsement_reject, promotion_return, promotion_status, discount_cap_return, commission_share_change, commission_rate_change, commission_reversal, commission_wht_change, scheme_end</t>
+    <t xml:space="preserve">decline, repudiation, lapse, refund, adjustment, non-materialise, reassignment, period_close, period_reopen, year_end_reverse, cas_print_void, cas_document_change, incentive_batch_reject, incentive_adjustment, year_end_cancel, remittance_reject, remittance_withdraw, remittance_cancel, remittance_revoke, remittance_off_cycle, remittance_line_exclude, exception_escalate, exception_resolve, exception_reopen, reconciliation_difference, reconciliation_unmatch, confirmation_difference, payment_duplicate_override, billing_reject, billing_cancel, sales_invoice_cancel, invoice_payment_cancel, delegation, delegation_end, sod_exception, access_review, data_load_reject, access_change, pdc_cancel, pdc_bounce, receipt_reversal, receipt_reversal_reject, unapplied_refund, renewal_reassign, non_renewal, claim_cancel, claim_cash_reversal, talkbot_line_remove, talkbot_list_cancel, feature_change, feature_reject, policy_suspend, policy_reinstate, policy_correction, policy_correction_reject, endorsement_reject, promotion_return, promotion_status, discount_cap_return, commission_share_change, commission_rate_change, commission_reversal, commission_wht_change, scheme_end, dealer_scheme_return, dealer_scheme_status, scheme_application_cancel, lockin_renew, lockin_hold, lockin_release, lockin_not_renewed, lockin_end, fmv_edit, rate_override, incentive_disqualify, incentive_exclude</t>
   </si>
   <si>
     <t xml:space="preserve">context</t>
